--- a/data/trans_camb/IP18_E_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP18_E_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 2,56</t>
+          <t>-7,23; 2,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 2,82</t>
+          <t>-6,47; 3,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,7; -1,03</t>
+          <t>-30,16; -1,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 11,57</t>
+          <t>0,43; 12,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 9,22</t>
+          <t>-3,89; 9,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 14,34</t>
+          <t>1,01; 13,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 5,65</t>
+          <t>-1,5; 6,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 4,6</t>
+          <t>-2,97; 4,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 4,69</t>
+          <t>-11,97; 4,45</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 2,6</t>
+          <t>-7,46; 2,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 3,02</t>
+          <t>-6,68; 3,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,05; -0,85</t>
+          <t>-31,33; -1,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 13,64</t>
+          <t>0,5; 14,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 10,94</t>
+          <t>-4,19; 10,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 16,9</t>
+          <t>1,2; 16,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 6,35</t>
+          <t>-1,6; 6,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 5,13</t>
+          <t>-3,18; 5,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 5,08</t>
+          <t>-12,95; 4,9</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 6,53</t>
+          <t>-0,18; 6,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 5,65</t>
+          <t>-2,29; 5,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 2,77</t>
+          <t>-17,89; 2,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 5,09</t>
+          <t>-1,55; 5,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,67</t>
+          <t>-2,12; 4,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 1,66</t>
+          <t>-19,2; 2,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 4,75</t>
+          <t>-0,1; 4,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,0</t>
+          <t>-0,94; 3,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 0,51</t>
+          <t>-15,39; -0,12</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 7,22</t>
+          <t>-0,17; 7,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 6,26</t>
+          <t>-2,4; 5,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 3,08</t>
+          <t>-19,37; 2,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 5,48</t>
+          <t>-1,62; 5,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 5,05</t>
+          <t>-2,24; 5,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 1,68</t>
+          <t>-20,55; 2,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,2</t>
+          <t>-0,13; 5,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 4,41</t>
+          <t>-1,0; 4,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 0,5</t>
+          <t>-16,43; -0,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 6,57</t>
+          <t>-3,81; 6,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 5,05</t>
+          <t>-5,07; 4,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-39,79; -2,71</t>
+          <t>-35,92; -1,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 4,36</t>
+          <t>-6,69; 4,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 5,55</t>
+          <t>-3,44; 5,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 8,79</t>
+          <t>-0,84; 8,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 3,53</t>
+          <t>-3,38; 3,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 3,42</t>
+          <t>-2,95; 3,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-21,1; 1,99</t>
+          <t>-19,02; 1,65</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 7,35</t>
+          <t>-4,0; 6,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 5,7</t>
+          <t>-5,32; 5,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-42,35; -2,93</t>
+          <t>-38,82; -1,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 4,78</t>
+          <t>-6,91; 4,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 6,04</t>
+          <t>-3,54; 6,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 9,75</t>
+          <t>-0,81; 9,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 3,81</t>
+          <t>-3,56; 3,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 3,77</t>
+          <t>-3,09; 3,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 2,14</t>
+          <t>-20,26; 1,67</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 5,52</t>
+          <t>-3,48; 5,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 5,74</t>
+          <t>-3,18; 5,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 3,98</t>
+          <t>-16,41; 4,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 4,97</t>
+          <t>-3,37; 5,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 4,31</t>
+          <t>-4,52; 3,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 5,26</t>
+          <t>-9,71; 5,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 4,02</t>
+          <t>-2,01; 3,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 3,86</t>
+          <t>-2,51; 3,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 3,54</t>
+          <t>-8,44; 3,06</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 6,1</t>
+          <t>-3,57; 5,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 6,39</t>
+          <t>-3,32; 5,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 4,27</t>
+          <t>-17,32; 4,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 5,44</t>
+          <t>-3,52; 5,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 4,69</t>
+          <t>-4,78; 4,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 5,79</t>
+          <t>-10,28; 5,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 4,37</t>
+          <t>-2,11; 4,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 4,22</t>
+          <t>-2,62; 4,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 3,87</t>
+          <t>-8,98; 3,3</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,47</t>
+          <t>-1,15; 3,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 2,89</t>
+          <t>-1,78; 2,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,39; -3,99</t>
+          <t>-20,09; -3,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,77</t>
+          <t>-0,57; 3,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,07</t>
+          <t>-1,09; 3,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 4,23</t>
+          <t>-3,54; 3,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,0</t>
+          <t>-0,01; 3,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,32</t>
+          <t>-0,86; 2,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -0,4</t>
+          <t>-8,49; -0,35</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,82</t>
+          <t>-1,21; 3,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,16</t>
+          <t>-1,89; 2,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,6; -4,32</t>
+          <t>-21,28; -3,98</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,1</t>
+          <t>-0,59; 4,22</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,36</t>
+          <t>-1,16; 3,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 4,58</t>
+          <t>-3,78; 4,27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,25</t>
+          <t>-0,01; 3,39</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,5</t>
+          <t>-0,9; 2,54</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,72; -0,44</t>
+          <t>-9,13; -0,38</t>
         </is>
       </c>
     </row>
